--- a/data/trans_dic/IP11A_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP11A_R-Edad-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -654,27 +654,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>6,96%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 30,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,65</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,8</t>
+          <t>0,0; 16,11</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -789,62 +789,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>3,03%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2,22%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>12,09%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>3,84%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>3,03%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2,22%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2,86%</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>12,56%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>2,86%</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>6,83%</t>
         </is>
       </c>
     </row>
@@ -857,12 +857,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 16,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,68</t>
+          <t>0,0; 11,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -872,17 +872,17 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 54,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,11</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,38</t>
+          <t>0,0; 15,56</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -892,17 +892,17 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,2</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,55</t>
+          <t>0,0; 8,58</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,09</t>
+          <t>0,0; 10,01</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,6</t>
+          <t>0,0; 34,69</t>
         </is>
       </c>
     </row>
@@ -934,44 +934,44 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>10,05%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>13,14%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>20,07%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>15,46%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>13,99%</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>10,05%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>13,14%</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
           <t>5,39%</t>
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,48%</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 42,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,67</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 62,35</t>
+          <t>0,0; 55,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,23</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 62,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,26</t>
+          <t>0,0; 54,59</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1042,17 +1042,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,51</t>
+          <t>0,0; 22,79</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,38</t>
+          <t>0,0; 21,2</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,34</t>
+          <t>0,0; 41,76</t>
         </is>
       </c>
     </row>
@@ -1069,54 +1069,54 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>10,82%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9,03%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>15,49%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7,56%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>10,82%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>7,34%</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>6,09%</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9,03%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>6,09%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
           <t>11,62%</t>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 33,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1147,17 +1147,17 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,59</t>
+          <t>0,0; 32,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,54</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1167,17 +1167,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,71</t>
+          <t>0,0; 39,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 35,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,49</t>
+          <t>0,0; 18,45</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,87; 26,35</t>
+          <t>3,01; 26,34</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,43</t>
+          <t>0,0; 19,35</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>3,92%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3,44%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>3,19%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>7,0%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>1,37%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>11,77%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>7,83%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3,92%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>3,44%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>3,19%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,2%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,04; 10,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,19</t>
+          <t>0,85; 9,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,27; 26,87</t>
+          <t>0,0; 9,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,91</t>
+          <t>0,0; 24,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,03; 10,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,86; 10,72</t>
+          <t>0,0; 6,85</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,92</t>
+          <t>3,33; 26,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,22</t>
+          <t>0,0; 23,6</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,59; 6,23</t>
+          <t>0,6; 5,99</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,57; 6,65</t>
+          <t>0,57; 6,51</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,22; 11,58</t>
+          <t>2,23; 13,12</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,49; 17,59</t>
+          <t>2,51; 16,81</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>641</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2852</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 2638</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 3546</t>
+          <t>0; 3209</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -1732,19 +1732,19 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,49 +1785,49 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>487</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>628</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>569</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
           <t>710</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>487</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>628</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>698</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>487</t>
-        </is>
-      </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
           <t>1338</t>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>568</t>
         </is>
       </c>
     </row>
@@ -1853,12 +1853,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2610</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2897</t>
+          <t>0; 3311</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1868,17 +1868,17 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2578</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 2587</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 2647</t>
+          <t>0; 2875</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1888,17 +1888,17 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3068</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 2514</t>
+          <t>0; 2526</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 4714</t>
+          <t>0; 4674</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 2931</t>
+          <t>0; 2889</t>
         </is>
       </c>
     </row>
@@ -1930,32 +1930,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1998,49 +1998,49 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1251</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>988</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
           <t>1257</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>754</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>689</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>1251</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>1012</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>1251</t>
-        </is>
-      </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
           <t>1257</t>
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1766</t>
+          <t>1677</t>
         </is>
       </c>
     </row>
@@ -2066,17 +2066,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 5300</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3300</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3041</t>
+          <t>0; 4172</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2086,17 +2086,17 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4637</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3935</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4256</t>
+          <t>0; 2687</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2106,17 +2106,17 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 5696</t>
+          <t>0; 5294</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 3946</t>
+          <t>0; 3914</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 5704</t>
+          <t>0; 5196</t>
         </is>
       </c>
     </row>
@@ -2133,7 +2133,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -2148,27 +2148,27 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1339</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -2211,39 +2211,39 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>1301</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
           <t>1493</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>590</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>592</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>1339</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1301</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>1339</t>
-        </is>
-      </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>592</t>
         </is>
       </c>
     </row>
@@ -2269,7 +2269,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4128</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2279,17 +2279,17 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3816</t>
+          <t>0; 4745</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3785</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4210</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2299,17 +2299,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4138</t>
+          <t>0; 3806</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2865</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 4285</t>
+          <t>0; 4057</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -2319,12 +2319,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>691; 6338</t>
+          <t>724; 6337</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 2831</t>
+          <t>0; 3271</t>
         </is>
       </c>
     </row>
@@ -2341,37 +2341,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2409,49 +2409,49 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1826</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>2521</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1301</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1557</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
           <t>710</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>2751</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>1344</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1281</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>1826</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>2521</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>1301</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1710</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>1826</t>
-        </is>
-      </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
           <t>3230</t>
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3054</t>
+          <t>2838</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>485; 4975</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 4234</t>
+          <t>626; 7305</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>765; 6280</t>
+          <t>0; 4004</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 4444</t>
+          <t>0; 5363</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>481; 4861</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>632; 7867</t>
+          <t>0; 3544</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 4041</t>
+          <t>778; 6218</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 5821</t>
+          <t>0; 4055</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>485; 5099</t>
+          <t>488; 4903</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>712; 8323</t>
+          <t>713; 8145</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1426; 7423</t>
+          <t>1428; 8407</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1024; 7244</t>
+          <t>990; 6628</t>
         </is>
       </c>
     </row>
